--- a/IRP_타겟고객_룰베이스_v1.xlsx
+++ b/IRP_타겟고객_룰베이스_v1.xlsx
@@ -9109,7 +9109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9686,6 +9686,58 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BS-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ISA 만기자금 보유</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>isa_days_to_maturity &gt;= -60</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>isa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TG-005</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>지식베이스 세그먼트 17 «ISA 만기 도래(예정) 또는 만기해지 후 60일 미경과»</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>에이전트 초안(기획자 위임 2026-10-22) — 기획자 검토 전</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>만기 예정 + 만기 후 60일 이내(IRP 전환 특례 기한과 같다). ISA 는 IRP 밖 계좌</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ISA 만기; ISA 만기자금; ISA 만기 고객</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9697,7 +9749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10280,6 +10332,44 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BS-11-C01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BS-11</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>isa_days_to_maturity</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>만기 예정 또는 만기 후 60일 이내</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IRP_타겟고객_룰베이스_v1.xlsx
+++ b/IRP_타겟고객_룰베이스_v1.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>평균 수익률 하락 AND BS-01 증가</t>
+          <t>부점 수익률 하락 AND BS-01 증가</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>평균 수익률 하락 AND BS-07 증가</t>
+          <t>부점 수익률 하락 AND BS-07 증가</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>같은 CASE_ID 의 행은 전부 AND. 대상구분 지표 = 부점 지표(total_eval_amt · customer_count · avg_return_rate), 세그먼트 = 부점세그먼트_Master 의 SEG_ID. 방향 증가·감소의 최소 변화폭은 부점_임계값 시트.</t>
+          <t>같은 CASE_ID 의 행은 전부 AND. 대상구분 지표 = 부점 지표(total_eval_amt 부점 잔액 · customer_count 계좌 수 · branch_return_rate 부점 수익률(적립금 가중)), 세그먼트 = 부점세그먼트_Master 의 SEG_ID. 방향 증가·감소의 최소 변화폭은 부점_임계값 시트.</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>avg_return_rate</t>
+          <t>branch_return_rate</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>평균 수익률 하락</t>
+          <t>부점 수익률 하락</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>avg_return_rate</t>
+          <t>branch_return_rate</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>평균 수익률 하락</t>
+          <t>부점 수익률 하락</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>평균 수익률 변화 최소 폭</t>
+          <t>부점 수익률 변화 최소 폭</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>전월말 대비 이만큼 이상 내리면 «하락»(감소)</t>
+          <t>부점 수익률 = 적립금 가중 수익률. 전월말 대비 이만큼 이상 내리면 «하락»(감소)</t>
         </is>
       </c>
     </row>
@@ -2066,6 +2066,96 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-22 결정 — 오늘 기준 직전 달 말일 스냅샷과 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BP-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>비중 지표 변화 최소 폭</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>%p</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>원리금보장 비중·고액 적립금 비중의 증가·감소 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BP-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>수익률 저조 기준</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1년 수익률이 이 값 미만이면 «수익률 저조 고객»(부점 브리핑 화면 기획안)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BP-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>고액 적립금 기준</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>평가금액이 이 값 이상이면 «적립금 1억 이상 고객»(부점 브리핑 화면 기획안)</t>
         </is>
       </c>
     </row>

--- a/IRP_타겟고객_룰베이스_v1.xlsx
+++ b/IRP_타겟고객_룰베이스_v1.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점세그먼트_조건" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점CASE_Rule" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점CASE_조건" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점_임계값" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점CASE_중점조건" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부점_임계값" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'타겟_Master'!$A$4:$V$18</definedName>
@@ -1835,6 +1836,854 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>부점 CASE 중점관리 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>오늘의 중점관리 고객 = 관리 대상(타겟 요건 1개 이상) 중 오늘 성립한 CASE 의 «우선관리 고객 특징»을 전부 만족하는 고객. 같은 CASE_ID 의 행은 전부 AND, CASE 가 여럿이면 CASE 사이는 OR. 조건 필드는 부점 DB 고정 뷰(v_irp_customer) 컬럼 이름이고 연산자는 &gt;= · &lt;= · = 만 쓴다. 금액·기간 임계는 원문에 없어 D(설계 제안) — 실서비스에서는 부점 규모·상황에 맞게 조정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>FCOND_ID</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>CASE_ID</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>조건필드</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>연산자</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>조건값</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>근거등급</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>설계·검토 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BC-01-F01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>days_to_maturity</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>만기 30일 이내(지난 만기 제외)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BS-04 와 같은 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BC-01-F02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>days_to_maturity</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>만기 30일 이내</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BS-04 와 같은 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BC-01-F03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>next_maturity_amt</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>만기금액 1천만원 이상</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>«만기금액이 크고»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BC-01-F04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>last_contact_days</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>마지막 접촉 후 90일 이상</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>«최근 접촉이 없었던» — 만기가 한 달 안이라 장기 미접촉 180일보다 짧게</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BC-02-F01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BC-02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>idle_cash_pct</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>고유계정대 비중 50% 이상</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>«현금 비중이 높은» — TG-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BC-02-F02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BC-02</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>idle_cash_days</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60일 이상 미운용</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>«미운용 기간이 길고» — BS-03 과 같은 60일</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BC-03-F01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BC-03</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>tax_credit_room</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>올해 세액공제 잔여한도 900만원(올해 납입 없음)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>«잔여한도가 크지만 최근 추가입금이 없고» — 추가입금 이력 컬럼이 없어 한도가 그대로 남은 것으로 본다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BC-03-F02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BC-03</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pension_started</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>미개시</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>연금 미개시</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>연금 개시 계좌는 추가입금 불가(방법론 59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BC-03-F03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BC-03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>last_contact_days</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>180</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>마지막 접촉 후 180일 이상</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>«접촉이 오래된» — 요건 «장기 미접촉»과 같은 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BC-03-F04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BC-03</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>eval_amt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>평가금액 3천만원 이상</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>추가입금 상담 실익 — 기획자 CASE 특징에는 없는 에이전트 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BC-04-F01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BC-04</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>risk_mismatch</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>불일치</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>투자성향 불일치</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>«투자성향 변경 후에도 기존 상품을 유지» — 성향 변경 이력 컬럼이 없어 불일치로 본다</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BC-04-F02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BC-04</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>safe_asset_pct</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>원리금보장 비중 80% 이상</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>«원리금보장상품에 편중» — BS-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BC-05-F01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BC-05</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>pension_eligible</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>충족</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>연금개시 요건 충족</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BS-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BC-05-F02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BC-05</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pension_started</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>미개시</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>A. 문서 직접명시</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>연금 미개시</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BS-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BC-05-F03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BC-05</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>eval_amt</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>평가금액 1억원 이상</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>«IRP 평가금액이 크고» — 고액 적립금 기준 BP-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BC-05-F04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BC-05</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>last_contact_days</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>180</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>마지막 접촉 후 180일 이상</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>«최근 상담이 없었던»</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/IRP_타겟고객_룰베이스_v1.xlsx
+++ b/IRP_타겟고객_룰베이스_v1.xlsx
@@ -2684,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3005,6 +3005,66 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>평가금액이 이 값 이상이면 «적립금 1억 이상 고객»(부점 브리핑 화면 기획안)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BP-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>오늘의 중점관리 고객 최대 인원</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-22 사용자 결정 «부점별 상한은 100명까지». 중점관리 조건을 갖춘 고객이 더 많으면 우선순위 앞쪽만 싣고 전체 인원을 밝힌다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BP-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>중점관리 고객이 없을 때 싣는 인원</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>D. 설계 제안 포함</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>오늘 CASE 가 없거나 CASE 조건을 모두 갖춘 고객이 0명이면, 중점관리 고객이 아님을 밝히고 관리 대상을 우선순위 앞쪽부터 이 인원만</t>
         </is>
       </c>
     </row>
